--- a/output/full_scan/batch_seq8_2026-07-03.xlsx
+++ b/output/full_scan/batch_seq8_2026-07-03.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O125"/>
+  <dimension ref="A1:O128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>8042</v>
+        <v>7610</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>金山電</t>
+          <t>聯友金屬-創</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>894.7959055492685</v>
+        <v>1041.347589877544</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>210.5</v>
+        <v>2550</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>66.5133462824537</v>
+        <v>71.0361673756166</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>30.45185396010869</v>
+        <v>45.49882085223157</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>5.369253562974621</v>
+        <v>0.4776272184754687</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-0.1655961315463798</v>
+        <v>3.652040812904261</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>7828</v>
+        <v>8042</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>創新服務</t>
+          <t>金山電</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>847.6366158352108</v>
+        <v>894.7959055492685</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2200</v>
+        <v>210.5</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>60.60533745445607</v>
+        <v>66.5133462824537</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>31.33859997675333</v>
+        <v>30.45185396010869</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2.725969921358165</v>
+        <v>5.369253562974621</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>-4.021654577494871</v>
+        <v>-0.1655961315463798</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6907</v>
+        <v>8033</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>雅特力-KY</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>834.4467035792713</v>
+        <v>875.4794879563752</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>170.5</v>
+        <v>204.5</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>64.70468625518896</v>
+        <v>84.59059787422042</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>30.57030709082996</v>
+        <v>27.13413557716127</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.6248728802443169</v>
+        <v>1.147948795637524</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1.196539127536824</v>
+        <v>7.663533939725161</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>7795</v>
+        <v>7828</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>長廣</t>
+          <t>創新服務</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>774.3875694244155</v>
+        <v>847.6366158352108</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>626</v>
+        <v>2200</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>79.94383968667145</v>
+        <v>60.60533745445607</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>29.43458712480011</v>
+        <v>31.33859997675333</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.038756942441544</v>
+        <v>2.725969921358165</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>24.13371809478319</v>
+        <v>-4.021654577494871</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7402</v>
+        <v>6907</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>雅特力-KY</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>756.6313261422011</v>
+        <v>834.4467035792713</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>138.5</v>
+        <v>170.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>80.78930467391362</v>
+        <v>64.70468625518896</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>27.38326611266448</v>
+        <v>30.57030709082996</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>4.263132614220118</v>
+        <v>0.6248728802443169</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>4.89078394698518</v>
+        <v>1.196539127536824</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>8028</v>
+        <v>7795</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>長廣</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>738.0649257335625</v>
+        <v>774.3875694244155</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>334.5</v>
+        <v>626</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>60.74148489007833</v>
+        <v>79.94383968667145</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>30.43739565773366</v>
+        <v>29.43458712480011</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.592870928844595</v>
+        <v>2.038756942441544</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.5921495124281346</v>
+        <v>24.13371809478319</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6870</v>
+        <v>7402</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>騰雲</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>717.0911976482446</v>
+        <v>756.6313261422011</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>310</v>
+        <v>138.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>61.86388942980496</v>
+        <v>80.78930467391362</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>22.62134633309001</v>
+        <v>27.38326611266448</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.7139476291218581</v>
+        <v>4.263132614220118</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.6143474429715319</v>
+        <v>4.89078394698518</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6949</v>
+        <v>8028</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沛爾生醫-創</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>688.3529814658718</v>
+        <v>738.0649257335625</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>916</v>
+        <v>334.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>67.19210700559094</v>
+        <v>60.74148489007833</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>35.28595583722488</v>
+        <v>30.43739565773366</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.6538384946160744</v>
+        <v>1.592870928844595</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>6.020030244157937</v>
+        <v>-0.5921495124281346</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6957</v>
+        <v>6870</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>裕慶-KY</t>
+          <t>騰雲</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>683.3927251879693</v>
+        <v>717.0911976482446</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>193</v>
+        <v>310</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>61.07746384215383</v>
+        <v>61.86388942980496</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>20.3748021883561</v>
+        <v>22.62134633309001</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.162842594908681</v>
+        <v>0.7139476291218581</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-0.9239226829671896</v>
+        <v>0.6143474429715319</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>8043</v>
+        <v>6949</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>沛爾生醫-創</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>666.8418639599726</v>
+        <v>688.3529814658718</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>202.5</v>
+        <v>916</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>58.49271016050272</v>
+        <v>67.19210700559094</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>32.7456558670286</v>
+        <v>35.28595583722488</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.077399954571009</v>
+        <v>0.6538384946160744</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-3.514263820449163</v>
+        <v>6.020030244157937</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6901</v>
+        <v>6957</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>鑽石投資</t>
+          <t>裕慶-KY</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>666.8388061596409</v>
+        <v>683.3927251879693</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>18.9</v>
+        <v>193</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>66.89670531517979</v>
+        <v>61.07746384215383</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>47.88367372858865</v>
+        <v>20.3748021883561</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.179628113560122</v>
+        <v>1.162842594908681</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.1113783087073403</v>
+        <v>-0.9239226829671896</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6996</v>
+        <v>8043</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>力領科技</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>666.0957260968295</v>
+        <v>666.8418639599726</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>201</v>
+        <v>202.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>58.58388046551645</v>
+        <v>58.49271016050272</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>20.59137389434822</v>
+        <v>32.7456558670286</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.300233244689456</v>
+        <v>1.077399954571009</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-0.114598838289718</v>
+        <v>-3.514263820449163</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>7714</v>
+        <v>6901</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>創泓科技</t>
+          <t>鑽石投資</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>659.9847113764147</v>
+        <v>666.8388061596409</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>159.5</v>
+        <v>18.9</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>70.79722004596954</v>
+        <v>66.89670531517979</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>29.05636904155603</v>
+        <v>47.88367372858865</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>3.421444202313458</v>
+        <v>1.179628113560122</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>2.939111607661317</v>
+        <v>0.1113783087073403</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6928</v>
+        <v>6996</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>力領科技</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>657.449118623898</v>
+        <v>666.0957260968295</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>57.6</v>
+        <v>201</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>71.58062006211513</v>
+        <v>58.58388046551645</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>30.99078451027948</v>
+        <v>20.59137389434822</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>4.3449118623898</v>
+        <v>1.300233244689456</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.9354598585777472</v>
+        <v>-0.114598838289718</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6994</v>
+        <v>7714</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>富威電力</t>
+          <t>創泓科技</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>644</v>
+        <v>659.9847113764147</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>41.9</v>
+        <v>159.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>24.84326005736617</v>
+        <v>70.79722004596954</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>31.73524442429009</v>
+        <v>29.05636904155603</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>7.079578610799402</v>
+        <v>3.421444202313458</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-1.112808194677436</v>
+        <v>2.939111607661317</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>8016</v>
+        <v>6928</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>643.5762349384155</v>
+        <v>657.449118623898</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>334</v>
+        <v>57.6</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>62.31319071679082</v>
+        <v>71.58062006211513</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>36.05514321821117</v>
+        <v>30.99078451027948</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.5375132193766063</v>
+        <v>4.3449118623898</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>1.674646573156934</v>
+        <v>0.9354598585777472</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6967</v>
+        <v>6994</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>635.4400756145354</v>
+        <v>644</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>74</v>
+        <v>41.9</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>57.39225829278539</v>
+        <v>24.84326005736617</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>11.88197214989092</v>
+        <v>31.73524442429009</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.902143863509867</v>
+        <v>7.079578610799402</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.3444426585739212</v>
+        <v>-1.112808194677436</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>8046</v>
+        <v>8016</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>632.7604491057364</v>
+        <v>643.5762349384155</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1185</v>
+        <v>334</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>68.70876517049993</v>
+        <v>62.31319071679082</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>22.44590490485973</v>
+        <v>36.05514321821117</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.6959226379763962</v>
+        <v>0.5375132193766063</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>27.51883025104584</v>
+        <v>1.674646573156934</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>7820</v>
+        <v>6967</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>627.0247188317468</v>
+        <v>635.4400756145354</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>53.28351536517937</v>
+        <v>57.39225829278539</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>25.60468238861493</v>
+        <v>11.88197214989092</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>2.071522652811332</v>
+        <v>1.902143863509867</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1.546610825450348</v>
+        <v>0.3444426585739212</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>7556</v>
+        <v>8046</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>618.1740023707912</v>
+        <v>632.7604491057364</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>291.5</v>
+        <v>1185</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>57.99171488067685</v>
+        <v>68.70876517049993</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>12.9197629031974</v>
+        <v>22.44590490485973</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.8662696218111564</v>
+        <v>0.6959226379763962</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.7746953742819631</v>
+        <v>27.51883025104584</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, foreign_buy_3d, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8040</v>
+        <v>7820</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>600.5023561082724</v>
+        <v>627.0247188317468</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>102.5</v>
+        <v>124</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>50.44319839513732</v>
+        <v>53.28351536517937</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>33.40681901127267</v>
+        <v>25.60468238861493</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.3509689308501284</v>
+        <v>2.071522652811332</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-1.041523222243255</v>
+        <v>1.546610825450348</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>7631</v>
+        <v>7556</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>597.5493416400453</v>
+        <v>618.1740023707912</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>160.5</v>
+        <v>291.5</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>58.18797339793228</v>
+        <v>57.99171488067685</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>18.50931569701365</v>
+        <v>12.9197629031974</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.5037449823109809</v>
+        <v>0.8662696218111564</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>2.144714668672337</v>
+        <v>0.7746953742819631</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, foreign_buy_3d, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>7818</v>
+        <v>8040</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>567.7550058619821</v>
+        <v>600.5023561082724</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>68.8</v>
+        <v>102.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>54.10676325289534</v>
+        <v>50.44319839513732</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>39.00790957762243</v>
+        <v>33.40681901127267</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.699108586441732</v>
+        <v>0.3509689308501284</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>1.792758030057548</v>
+        <v>-1.041523222243255</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6916</v>
+        <v>7631</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>530.886628153926</v>
+        <v>597.5493416400453</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>20.8</v>
+        <v>160.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>54.31431824359207</v>
+        <v>58.18797339793228</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>22.74664568715254</v>
+        <v>18.50931569701365</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.4150405367626503</v>
+        <v>0.5037449823109809</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.1774651189080996</v>
+        <v>2.144714668672337</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6971</v>
+        <v>7818</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>511.4771424579681</v>
+        <v>567.7550058619821</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>27.85</v>
+        <v>68.8</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>52.91514678424359</v>
+        <v>54.10676325289534</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>22.43080896943357</v>
+        <v>39.00790957762243</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.5944977709351487</v>
+        <v>1.699108586441732</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.06347649824472271</v>
+        <v>1.792758030057548</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>volume_break, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6922</v>
+        <v>6916</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>宸曜</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>511.3470463820169</v>
+        <v>530.886628153926</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>186</v>
+        <v>20.8</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>52.98710666938754</v>
+        <v>54.31431824359207</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>15.19000917330035</v>
+        <v>22.74664568715254</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.5511156189462062</v>
+        <v>0.4150405367626503</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.5569247915804538</v>
+        <v>-0.1774651189080996</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6937</v>
+        <v>6971</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>惠民實業</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>510.557028071657</v>
+        <v>511.4771424579681</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>287</v>
+        <v>27.85</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>52.61112810887225</v>
+        <v>52.91514678424359</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>13.47661091741611</v>
+        <v>22.43080896943357</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.841478488541941</v>
+        <v>0.5944977709351487</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>2.361362357096387</v>
+        <v>0.06347649824472271</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>7715</v>
+        <v>6922</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>裕山</t>
+          <t>宸曜</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>503.7872641589453</v>
+        <v>511.3470463820169</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>36</v>
+        <v>186</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>64.72306434612267</v>
+        <v>52.98710666938754</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>46.08066722366417</v>
+        <v>15.19000917330035</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.2400780655422492</v>
+        <v>0.5511156189462062</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.3147927462127426</v>
+        <v>-0.5569247915804538</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8032</v>
+        <v>6937</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>502.5110470690304</v>
+        <v>510.557028071657</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>43.4</v>
+        <v>287</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>47.1846617542988</v>
+        <v>52.61112810887225</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>20.19995519094418</v>
+        <v>13.47661091741611</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.1653516957382273</v>
+        <v>1.841478488541941</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.4601450060625426</v>
+        <v>2.361362357096387</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>7705</v>
+        <v>8021</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>三商餐飲</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>501.5385647743332</v>
+        <v>505.5519790810167</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>32.9</v>
+        <v>558</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>64.33360956613794</v>
+        <v>57.39033799585067</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>18.24421614775154</v>
+        <v>22.61521680327542</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>3.029034970808611</v>
+        <v>0.2222310127447941</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.1687298351847226</v>
+        <v>-3.567609060197402</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>7788</v>
+        <v>7715</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>498.3764700477989</v>
+        <v>503.7872641589453</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>246.5</v>
+        <v>36</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>51.53359597357016</v>
+        <v>64.72306434612267</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>34.04943251279816</v>
+        <v>46.08066722366417</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.2281745145216304</v>
+        <v>0.2400780655422492</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-5.296872996031745</v>
+        <v>0.3147927462127426</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6890</v>
+        <v>8032</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>494.9518407498683</v>
+        <v>502.5110470690304</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>212</v>
+        <v>43.4</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>48.96566363389418</v>
+        <v>47.1846617542988</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>22.94661385799666</v>
+        <v>20.19995519094418</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.4607898193624773</v>
+        <v>0.1653516957382273</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-6.960023832028796</v>
+        <v>-0.4601450060625426</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6944</v>
+        <v>7705</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>三商餐飲</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>491.3582735136993</v>
+        <v>501.5385647743332</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>992</v>
+        <v>32.9</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>53.10557197668399</v>
+        <v>64.33360956613794</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>13.92179382522848</v>
+        <v>18.24421614775154</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.450620066157962</v>
+        <v>3.029034970808611</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-4.516815224258547</v>
+        <v>0.1687298351847226</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>8044</v>
+        <v>7788</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>491.0504138169626</v>
+        <v>498.3764700477989</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>28.15</v>
+        <v>246.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>47.43262142085686</v>
+        <v>51.53359597357016</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>16.38992532811137</v>
+        <v>34.04943251279816</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.4074287048939343</v>
+        <v>0.2281745145216304</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.4171607688895083</v>
+        <v>-5.296872996031745</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6862</v>
+        <v>6890</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>486.613755664652</v>
+        <v>494.9518407498683</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>49.75090646284125</v>
+        <v>48.96566363389418</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>20.86633165915518</v>
+        <v>22.94661385799666</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.4146508150921312</v>
+        <v>0.4607898193624773</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-1.899887944703305</v>
+        <v>-6.960023832028796</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6914</v>
+        <v>6944</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>阜爾運通</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>478.5287742732157</v>
+        <v>491.3582735136993</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>145</v>
+        <v>992</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>60.39231639893473</v>
+        <v>53.10557197668399</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>10.51311092033501</v>
+        <v>13.92179382522848</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.139809653036015</v>
+        <v>0.450620066157962</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.3755190218230994</v>
+        <v>-4.516815224258547</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8039</v>
+        <v>8044</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>477.488113093309</v>
+        <v>491.0504138169626</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>151</v>
+        <v>28.15</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>55.17255635238659</v>
+        <v>47.43262142085686</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>17.65370876125903</v>
+        <v>16.38992532811137</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.046353981325801</v>
+        <v>0.4074287048939343</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.4197352578849139</v>
+        <v>-0.4171607688895083</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>7722</v>
+        <v>6862</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>LINEPAY</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>454.5125212961813</v>
+        <v>486.613755664652</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>314.5</v>
+        <v>195</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>51.68381309120011</v>
+        <v>49.75090646284125</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>34.71095539887571</v>
+        <v>20.86633165915518</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.1945359969461345</v>
+        <v>0.4146508150921312</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-2.108065751354877</v>
+        <v>-1.899887944703305</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6903</v>
+        <v>6914</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>阜爾運通</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>445.9486110602965</v>
+        <v>478.5287742732157</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>404</v>
+        <v>145</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>54.30768439494493</v>
+        <v>60.39231639893473</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>10.22955284695407</v>
+        <v>10.51311092033501</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.421809599275291</v>
+        <v>1.139809653036015</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>2.161504396439673</v>
+        <v>0.3755190218230994</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>7770</v>
+        <v>8039</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>440.5894591037542</v>
+        <v>477.488113093309</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>42.55</v>
+        <v>151</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>49.64989129859116</v>
+        <v>55.17255635238659</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>5.471679640939136</v>
+        <v>17.65370876125903</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>2.270564993613672</v>
+        <v>1.046353981325801</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.0262090475248971</v>
+        <v>0.4197352578849139</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6906</v>
+        <v>7722</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>LINEPAY</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>431.5412162231184</v>
+        <v>454.5125212961813</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>91.3</v>
+        <v>314.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>53.20467660880018</v>
+        <v>51.68381309120011</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>21.20680831371036</v>
+        <v>34.71095539887571</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.4689540309322161</v>
+        <v>0.1945359969461345</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.7226906122191301</v>
+        <v>-2.108065751354877</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6933</v>
+        <v>6903</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>AMAX-KY</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>428.825539045672</v>
+        <v>445.9486110602965</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>152</v>
+        <v>404</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>48.36139538031544</v>
+        <v>54.30768439494493</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>20.78117000799191</v>
+        <v>10.22955284695407</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.602373539620496</v>
+        <v>1.421809599275291</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.3234480754907389</v>
+        <v>2.161504396439673</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, hist_turn_positive, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>7704</v>
+        <v>7770</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>君曜</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>425.1322045331562</v>
+        <v>440.5894591037542</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>63.5</v>
+        <v>42.55</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>55.84255976324695</v>
+        <v>49.64989129859116</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>11.16338284643668</v>
+        <v>5.471679640939136</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.15271863662282</v>
+        <v>2.270564993613672</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>1</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.2728659954163246</v>
+        <v>0.0262090475248971</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>7842</v>
+        <v>6906</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>423.2143291246146</v>
+        <v>431.5412162231184</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>96.5</v>
+        <v>91.3</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>34.63355335825796</v>
+        <v>53.20467660880018</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>25.92714926804813</v>
+        <v>21.20680831371036</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.5122657866455957</v>
+        <v>0.4689540309322161</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.5776616877867626</v>
+        <v>-0.7226906122191301</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>7751</v>
+        <v>6933</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>421.3183944691492</v>
+        <v>428.825539045672</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>1440</v>
+        <v>152</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>45.44388334746257</v>
+        <v>48.36139538031544</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>11.39377743325952</v>
+        <v>20.78117000799191</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.3059914397558561</v>
+        <v>1.602373539620496</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>15.84593413929648</v>
+        <v>0.3234480754907389</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, hist_turn_positive, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6951</v>
+        <v>7704</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>417.0114159608102</v>
+        <v>425.1322045331562</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>79.09999999999999</v>
+        <v>63.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>49.90116158297625</v>
+        <v>55.84255976324695</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>24.8189746187682</v>
+        <v>11.16338284643668</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.4104692005106166</v>
+        <v>1.15271863662282</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.0672951172250246</v>
+        <v>0.2728659954163246</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6952</v>
+        <v>7842</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>大武山</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>415.3508701641822</v>
+        <v>423.2143291246146</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>35.35</v>
+        <v>96.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>34.84867940768721</v>
+        <v>34.63355335825796</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>21.05524742469282</v>
+        <v>25.92714926804813</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>2.148503641129606</v>
+        <v>0.5122657866455957</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.0300386638629545</v>
+        <v>0.5776616877867626</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>7799</v>
+        <v>7751</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>411.281561929504</v>
+        <v>421.3183944691492</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>391</v>
+        <v>1440</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>54.60371635329098</v>
+        <v>45.44388334746257</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>36.30084424788001</v>
+        <v>11.39377743325952</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.966726756952902</v>
+        <v>0.3059914397558561</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>1.33600286298525</v>
+        <v>15.84593413929648</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6919</v>
+        <v>6951</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>408.9199605973924</v>
+        <v>417.0114159608102</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>99.7</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>49.80492747170982</v>
+        <v>49.90116158297625</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>13.73408011948013</v>
+        <v>24.8189746187682</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.6447691082452494</v>
+        <v>0.4104692005106166</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.19326580733261</v>
+        <v>0.0672951172250246</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>7744</v>
+        <v>6952</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>崴寶</t>
+          <t>大武山</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>406.5146617704284</v>
+        <v>415.3508701641822</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>466.5</v>
+        <v>35.35</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>47.75264529006611</v>
+        <v>34.84867940768721</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>13.81091301444593</v>
+        <v>21.05524742469282</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.3741417538016001</v>
+        <v>2.148503641129606</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.3921663518231675</v>
+        <v>0.0300386638629545</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6902</v>
+        <v>7799</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>403.95729359385</v>
+        <v>411.281561929504</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>134</v>
+        <v>391</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>52.00109282834654</v>
+        <v>54.60371635329098</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>21.75640075804892</v>
+        <v>36.30084424788001</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.1992590228537333</v>
+        <v>0.966726756952902</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.8592614673874044</v>
+        <v>1.33600286298525</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>7760</v>
+        <v>6919</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>400.6060134101813</v>
+        <v>408.9199605973924</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>36.35</v>
+        <v>99.7</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>72.15197833293277</v>
+        <v>49.80492747170982</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>36.7089652718276</v>
+        <v>13.73408011948013</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.195977468511724</v>
+        <v>0.6447691082452494</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.468707748997776</v>
+        <v>-0.19326580733261</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6894</v>
+        <v>7744</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>崴寶</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>389.3574290809198</v>
+        <v>406.5146617704284</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>360.5</v>
+        <v>466.5</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>48.7464992528228</v>
+        <v>47.75264529006611</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>19.37989771046073</v>
+        <v>13.81091301444593</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.1584616907457856</v>
+        <v>0.3741417538016001</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-1.655000577314421</v>
+        <v>0.3921663518231675</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>7827</v>
+        <v>6902</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>386.4937917424568</v>
+        <v>403.95729359385</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>161.5</v>
+        <v>134</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>51.45506471350726</v>
+        <v>52.00109282834654</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>19.63758018845034</v>
+        <v>21.75640075804892</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.9231823547928808</v>
+        <v>0.1992590228537333</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.9405502784541636</v>
+        <v>-0.8592614673874044</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6958</v>
+        <v>7760</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>日盛台駿</t>
+          <t>享溫馨</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>384.795891728432</v>
+        <v>400.6060134101813</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>17</v>
+        <v>36.35</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>48.76703568344132</v>
+        <v>72.15197833293277</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>15.13628966865609</v>
+        <v>36.7089652718276</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.0792818188370398</v>
+        <v>1.195977468511724</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.0017130884862688</v>
+        <v>0.468707748997776</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6962</v>
+        <v>6894</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>奕力-KY</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>382.9973488369013</v>
+        <v>389.3574290809198</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>38.9</v>
+        <v>360.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>54.81139423878789</v>
+        <v>48.7464992528228</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>14.08515421542532</v>
+        <v>19.37989771046073</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.791106428351816</v>
+        <v>0.1584616907457856</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.0413833719625043</v>
+        <v>-1.655000577314421</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>7738</v>
+        <v>7827</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>東聯互動</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>371.5768006533447</v>
+        <v>386.4937917424568</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>170</v>
+        <v>161.5</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>50.92890130273715</v>
+        <v>51.45506471350726</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>20.62657271611888</v>
+        <v>19.63758018845034</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.4132814884922604</v>
+        <v>0.9231823547928808</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.0658041413792924</v>
+        <v>-0.9405502784541636</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6859</v>
+        <v>6958</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>日盛台駿</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>366.7152118731906</v>
+        <v>384.795891728432</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>124</v>
+        <v>17</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>47.16293817343863</v>
+        <v>48.76703568344132</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>20.04156037152038</v>
+        <v>15.13628966865609</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.2917006233650341</v>
+        <v>0.0792818188370398</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-1.205485559362608</v>
+        <v>0.0017130884862688</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>7792</v>
+        <v>6962</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>安葆</t>
+          <t>奕力-KY</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>361.503140460462</v>
+        <v>382.9973488369013</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>253.5</v>
+        <v>38.9</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>41.26147089066344</v>
+        <v>54.81139423878789</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>19.28623826704084</v>
+        <v>14.08515421542532</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.2378284320533358</v>
+        <v>0.791106428351816</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.1014420434686762</v>
+        <v>0.0413833719625043</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>7768</v>
+        <v>7738</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>東聯互動</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>359.4069491623053</v>
+        <v>371.5768006533447</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>362</v>
+        <v>170</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>47.78266767328372</v>
+        <v>50.92890130273715</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>22.17097254252639</v>
+        <v>20.62657271611888</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.9249535180696576</v>
+        <v>0.4132814884922604</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.7179780882573681</v>
+        <v>0.0658041413792924</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>7717</v>
+        <v>6859</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>356.6878354201376</v>
+        <v>366.7152118731906</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>462.5</v>
+        <v>124</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>36.87169052067319</v>
+        <v>47.16293817343863</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>22.40328105873663</v>
+        <v>20.04156037152038</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.7255793706687058</v>
+        <v>0.2917006233650341</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-4.957772577982553</v>
+        <v>-1.205485559362608</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>7822</v>
+        <v>7792</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>安葆</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>348.8163366337365</v>
+        <v>361.503140460462</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>1175</v>
+        <v>253.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>52.1623391249711</v>
+        <v>41.26147089066344</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>18.96530334513982</v>
+        <v>19.28623826704084</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.6192593468165722</v>
+        <v>0.2378284320533358</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>8.712706190606928</v>
+        <v>0.1014420434686762</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>7711</v>
+        <v>7768</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>永擎</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>346.4268864528593</v>
+        <v>359.4069491623053</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>324.5</v>
+        <v>362</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>38.69174438451108</v>
+        <v>47.78266767328372</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>21.0337777378516</v>
+        <v>22.17097254252639</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.3156717966321402</v>
+        <v>0.9249535180696576</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-3.173029168508327</v>
+        <v>-0.7179780882573681</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6983</v>
+        <v>7717</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>340.8545623835828</v>
+        <v>356.6878354201376</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>366</v>
+        <v>462.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>49.08649522305166</v>
+        <v>36.87169052067319</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>11.33899104390398</v>
+        <v>22.40328105873663</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.4854179030202065</v>
+        <v>0.7255793706687058</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>3.367195332656218</v>
+        <v>-4.957772577982553</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6909</v>
+        <v>7822</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>336.5538630799134</v>
+        <v>348.8163366337365</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>59.7</v>
+        <v>1175</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>60.53515191921301</v>
+        <v>52.1623391249711</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>19.21894800159532</v>
+        <v>18.96530334513982</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.7312420158678642</v>
+        <v>0.6192593468165722</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.9757514421443608</v>
+        <v>8.712706190606928</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>7805</v>
+        <v>7711</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>威聯通</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>326.1161181786287</v>
+        <v>346.4268864528593</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>668</v>
+        <v>324.5</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>39.07475082525483</v>
+        <v>38.69174438451108</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>27.29888350721118</v>
+        <v>21.0337777378516</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.5151607694106071</v>
+        <v>0.3156717966321402</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,7 +4015,7 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-1.757645511264702</v>
+        <v>-3.173029168508327</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4025,21 +4025,21 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>7734</v>
+        <v>6983</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>322.3738751276229</v>
+        <v>340.8545623835828</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>3190</v>
+        <v>366</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>48.86167671130486</v>
+        <v>49.08649522305166</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>15.29223754599834</v>
+        <v>11.33899104390398</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.3296497650559686</v>
+        <v>0.4854179030202065</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-7.19538198134515</v>
+        <v>3.367195332656218</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>7753</v>
+        <v>6909</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>322.1096893195092</v>
+        <v>336.5538630799134</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>42.3</v>
+        <v>59.7</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>48.6459091577695</v>
+        <v>60.53515191921301</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>20.72087215031259</v>
+        <v>19.21894800159532</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.3522530676350743</v>
+        <v>0.7312420158678642</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.0655118150412269</v>
+        <v>0.9757514421443608</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>8047</v>
+        <v>7805</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>314.8051375398722</v>
+        <v>326.1161181786287</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>47.05</v>
+        <v>668</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>45.8114542720426</v>
+        <v>39.07475082525483</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>5.828310154349102</v>
+        <v>27.29888350721118</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.1646559709714373</v>
+        <v>0.5151607694106071</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.2120237176547679</v>
+        <v>-1.757645511264702</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6863</v>
+        <v>7734</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>309.9940201012259</v>
+        <v>322.3738751276229</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>91.8</v>
+        <v>3190</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>36.50627897022024</v>
+        <v>48.86167671130486</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>24.87532237651106</v>
+        <v>15.29223754599834</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.9540160032011148</v>
+        <v>0.3296497650559686</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.182149979931093</v>
+        <v>-7.19538198134515</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6899</v>
+        <v>7753</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>星亞</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>307.622519479252</v>
+        <v>322.1096893195092</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>58.6</v>
+        <v>42.3</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>46.43146095642409</v>
+        <v>48.6459091577695</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>17.13060914408574</v>
+        <v>20.72087215031259</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.797358677436599</v>
+        <v>0.3522530676350743</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.4149449585678393</v>
+        <v>-0.0655118150412269</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>7821</v>
+        <v>8047</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>305.9402430430725</v>
+        <v>314.8051375398722</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>42.15</v>
+        <v>47.05</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>38.71652146730627</v>
+        <v>45.8114542720426</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>23.69296879949588</v>
+        <v>5.828310154349102</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.154893012855833</v>
+        <v>0.1646559709714373</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.0173981288512907</v>
+        <v>-0.2120237176547679</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6913</v>
+        <v>6863</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>鴻呈</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>303.1817145020648</v>
+        <v>309.9940201012259</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>123</v>
+        <v>91.8</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>46.29794639611118</v>
+        <v>36.50627897022024</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>17.40346466066014</v>
+        <v>24.87532237651106</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.6874259772207314</v>
+        <v>0.9540160032011148</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.2109727466211755</v>
+        <v>-0.182149979931093</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6965</v>
+        <v>6899</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>301.6263079535917</v>
+        <v>307.622519479252</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>78</v>
+        <v>58.6</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>43.17458316165754</v>
+        <v>46.43146095642409</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>24.52817375887894</v>
+        <v>17.13060914408574</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.6942327682556058</v>
+        <v>1.797358677436599</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.264408713855353</v>
+        <v>-0.4149449585678393</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6910</v>
+        <v>7821</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>300.5433809213517</v>
+        <v>305.9402430430725</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>27.4</v>
+        <v>42.15</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>41.76225125125965</v>
+        <v>38.71652146730627</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>13.33652013337198</v>
+        <v>23.69296879949588</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.417725259012911</v>
+        <v>1.154893012855833</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.0802760232412678</v>
+        <v>-0.0173981288512907</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>7786</v>
+        <v>6913</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>鴻呈</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>300.2129335481984</v>
+        <v>303.1817145020648</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>52.12758193913844</v>
+        <v>46.29794639611118</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>15.51883300378108</v>
+        <v>17.40346466066014</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.243204737557281</v>
+        <v>0.6874259772207314</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.0735073821223011</v>
+        <v>-0.2109727466211755</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6934</v>
+        <v>6965</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>心誠鎂</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>294.1943102971515</v>
+        <v>301.6263079535917</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>69.5</v>
+        <v>78</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>49.21651552624098</v>
+        <v>43.17458316165754</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>20.75739854475172</v>
+        <v>24.52817375887894</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.8584612037058764</v>
+        <v>0.6942327682556058</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.2952093729235239</v>
+        <v>-0.264408713855353</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6955</v>
+        <v>6910</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>邦睿生技-創</t>
+          <t>德鴻</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>278.2995861390464</v>
+        <v>300.5433809213517</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>120.5</v>
+        <v>27.4</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>49.10519597791093</v>
+        <v>41.76225125125965</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>8.865418904283596</v>
+        <v>13.33652013337198</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.267878511596102</v>
+        <v>1.417725259012911</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.3466346767180468</v>
+        <v>-0.0802760232412678</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6969</v>
+        <v>7786</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>成信實業*-創</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>275.1224147284468</v>
+        <v>300.2129335481984</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>25.85</v>
+        <v>126</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>48.27549404875366</v>
+        <v>52.12758193913844</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>32.22731869343558</v>
+        <v>15.51883300378108</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.963997622484503</v>
+        <v>1.243204737557281</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.0653486408362987</v>
+        <v>-0.0735073821223011</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, adx_trending, williams_r_recovery</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>7728</v>
+        <v>6934</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>心誠鎂</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>274.1862690591902</v>
+        <v>294.1943102971515</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>672</v>
+        <v>69.5</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>43.16536099652165</v>
+        <v>49.21651552624098</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>11.57499592435893</v>
+        <v>20.75739854475172</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.4625527832624241</v>
+        <v>0.8584612037058764</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-3.737075790830559</v>
+        <v>0.2952093729235239</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6854</v>
+        <v>6955</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>錼創科技-KY創</t>
+          <t>邦睿生技-創</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>274.1603678443212</v>
+        <v>278.2995861390464</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>123</v>
+        <v>120.5</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>38.15781018711014</v>
+        <v>49.10519597791093</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>21.21942986078509</v>
+        <v>8.865418904283596</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.310896999962806</v>
+        <v>1.267878511596102</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.0240501081738635</v>
+        <v>-0.3466346767180468</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>7772</v>
+        <v>6969</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>耀穎</t>
+          <t>成信實業*-創</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>273.5058140634478</v>
+        <v>275.1224147284468</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>131.5</v>
+        <v>25.85</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>41.38784346406978</v>
+        <v>48.27549404875366</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>8.880880133824055</v>
+        <v>32.22731869343558</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.4609307770065875</v>
+        <v>1.963997622484503</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.5398441225570174</v>
+        <v>-0.0653486408362987</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>volume_break, market_above_ma60, adx_trending, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>7703</v>
+        <v>7728</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>銳澤</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>271.3775442258691</v>
+        <v>274.1862690591902</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>199.5</v>
+        <v>672</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>45.56541275764901</v>
+        <v>43.16536099652165</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>11.04915945105315</v>
+        <v>11.57499592435893</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.156361183223273</v>
+        <v>0.4625527832624241</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>1</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.2708150339572008</v>
+        <v>-3.737075790830559</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>7769</v>
+        <v>6854</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>錼創科技-KY創</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>266.631390648742</v>
+        <v>274.1603678443212</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>6865</v>
+        <v>123</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>49.93635882478338</v>
+        <v>38.15781018711014</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>15.81208356163863</v>
+        <v>21.21942986078509</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.8972425056386585</v>
+        <v>0.310896999962806</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,28 +4969,28 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-47.10926342516053</v>
+        <v>-0.0240501081738635</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>7747</v>
+        <v>7772</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>耀穎</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>266.2728536498706</v>
+        <v>273.5058140634478</v>
       </c>
       <c r="E86" s="2" t="n">
         <v>131.5</v>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>54.22648041242711</v>
+        <v>41.38784346406978</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>4.405281802227788</v>
+        <v>8.880880133824055</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.1785808969342198</v>
+        <v>0.4609307770065875</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.238095034293599</v>
+        <v>-0.5398441225570174</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>8045</v>
+        <v>7703</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>264.4592762889333</v>
+        <v>271.3775442258691</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>61</v>
+        <v>199.5</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>43.47585414032427</v>
+        <v>45.56541275764901</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>11.48226524768242</v>
+        <v>11.04915945105315</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.7421740867627571</v>
+        <v>1.156361183223273</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,7 +5075,7 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.2877597417123527</v>
+        <v>-0.2708150339572008</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -5085,21 +5085,21 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6861</v>
+        <v>7769</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>睿生光電</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>262.7146338340736</v>
+        <v>266.631390648742</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>327.5</v>
+        <v>6865</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>46.28438391683706</v>
+        <v>49.93635882478338</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>17.12358161321642</v>
+        <v>15.81208356163863</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.3376987180234795</v>
+        <v>0.8972425056386585</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-1.884978131244619</v>
+        <v>-47.10926342516053</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6988</v>
+        <v>7747</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>威力暘-創</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>261.6007419954057</v>
+        <v>266.2728536498706</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>13.55</v>
+        <v>131.5</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>35.20515682287703</v>
+        <v>54.22648041242711</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>13.73763515360437</v>
+        <v>4.405281802227788</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.8676507686544915</v>
+        <v>0.1785808969342198</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0075787738030346</v>
+        <v>0.238095034293599</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>ema60_gt_ema120, market_above_ma60, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>7839</v>
+        <v>8045</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>達人網</t>
+          <t>達運光電</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>258.4534526210672</v>
+        <v>264.4592762889333</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>45.9</v>
+        <v>61</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>45.11016353047087</v>
+        <v>43.47585414032427</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>8.45729448130411</v>
+        <v>11.48226524768242</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.1967343032373362</v>
+        <v>0.7421740867627571</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.2191898813482948</v>
+        <v>0.2877597417123527</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>7547</v>
+        <v>6861</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>睿生光電</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>257.7464633436241</v>
+        <v>262.7146338340736</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>58.7</v>
+        <v>327.5</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>44.60010131183608</v>
+        <v>46.28438391683706</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>13.27427910545215</v>
+        <v>17.12358161321642</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.2475685958240027</v>
+        <v>0.3376987180234795</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.3802743954623881</v>
+        <v>-1.884978131244619</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, foreign_buy_3d, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6887</v>
+        <v>6988</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>威力暘-創</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>252.8236941241151</v>
+        <v>261.6007419954057</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>34</v>
+        <v>13.55</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>46.06344781209794</v>
+        <v>35.20515682287703</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>6.02274499055146</v>
+        <v>13.73763515360437</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>2.521789309111675</v>
+        <v>0.8676507686544915</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.0160520776605305</v>
+        <v>0.0075787738030346</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>7749</v>
+        <v>7839</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>251.8314709217811</v>
+        <v>258.4534526210672</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>432.5</v>
+        <v>45.9</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>40.20243454244132</v>
+        <v>45.11016353047087</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>16.78735840937368</v>
+        <v>8.45729448130411</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.2584412959131219</v>
+        <v>0.1967343032373362</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-5.682915582051665</v>
+        <v>-0.2191898813482948</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6869</v>
+        <v>7547</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>雲豹能源</t>
+          <t>碩網</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>251.3541325518772</v>
+        <v>257.7464633436241</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>70.90000000000001</v>
+        <v>58.7</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>36.84440703451945</v>
+        <v>44.60010131183608</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>28.1227836200678</v>
+        <v>13.27427910545215</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.986935545066247</v>
+        <v>0.2475685958240027</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.6273046491610796</v>
+        <v>0.3802743954623881</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>7810</v>
+        <v>6887</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>捷創科技</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>246.7864126337463</v>
+        <v>252.8236941241151</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>205</v>
+        <v>34</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>45.28842874286558</v>
+        <v>46.06344781209794</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>12.31187028244892</v>
+        <v>6.02274499055146</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.332458309071297</v>
+        <v>2.521789309111675</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.9615850967191076</v>
+        <v>-0.0160520776605305</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6931</v>
+        <v>7749</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>239.2154023670836</v>
+        <v>251.8314709217811</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>40.5</v>
+        <v>432.5</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>46.14435224772334</v>
+        <v>40.20243454244132</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>18.90322303583656</v>
+        <v>16.78735840937368</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.448536655018948</v>
+        <v>0.2584412959131219</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.1332831415516526</v>
+        <v>-5.682915582051665</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6953</v>
+        <v>6869</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>雲豹能源</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>233.7652318100766</v>
+        <v>251.3541325518772</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>238.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>50.78068701009278</v>
+        <v>36.84440703451945</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>14.93991469052295</v>
+        <v>28.1227836200678</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.4694347857264379</v>
+        <v>0.986935545066247</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>1.866737602855505</v>
+        <v>-0.6273046491610796</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6924</v>
+        <v>7810</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>榮惠-KY創</t>
+          <t>捷創科技</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>228.2999277328838</v>
+        <v>246.7864126337463</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>129.5</v>
+        <v>205</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>50.75655206482485</v>
+        <v>45.28842874286558</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>19.22809839741472</v>
+        <v>12.31187028244892</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.8929821976155892</v>
+        <v>0.332458309071297</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.5374124644324927</v>
+        <v>0.9615850967191076</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6865</v>
+        <v>6931</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>偉康科技</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>227.8341986652306</v>
+        <v>239.2154023670836</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>28.5</v>
+        <v>40.5</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>51.96247872855241</v>
+        <v>46.14435224772334</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>15.43576722464051</v>
+        <v>18.90322303583656</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.0251587053479685</v>
+        <v>1.448536655018948</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.5378297294710574</v>
+        <v>0.1332831415516526</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6921</v>
+        <v>6953</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>嘉雨思-創</t>
+          <t>家碩</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>219.368619048076</v>
+        <v>233.7652318100766</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>68.7</v>
+        <v>238.5</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>38.92943837935411</v>
+        <v>50.78068701009278</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>17.68460429279206</v>
+        <v>14.93991469052295</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.4343049842883785</v>
+        <v>0.4694347857264379</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.2286166760005388</v>
+        <v>1.866737602855505</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>7765</v>
+        <v>6924</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>216.3725253644933</v>
+        <v>228.2999277328838</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>222</v>
+        <v>129.5</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>37.56840364739835</v>
+        <v>50.75655206482485</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>25.76197963059441</v>
+        <v>19.22809839741472</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.6475372202262271</v>
+        <v>0.8929821976155892</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-1.866134535011144</v>
+        <v>-0.5374124644324927</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>8038</v>
+        <v>6865</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>偉康科技</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>215.5568288754205</v>
+        <v>227.8341986652306</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>40.15</v>
+        <v>28.5</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>47.65131632623464</v>
+        <v>51.96247872855241</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>6.795267021245061</v>
+        <v>15.43576722464051</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.5478853360697563</v>
+        <v>0.0251587053479685</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.0253454598029686</v>
+        <v>0.5378297294710574</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6855</v>
+        <v>6921</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>嘉雨思-創</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>211.7157055573561</v>
+        <v>219.368619048076</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>121</v>
+        <v>68.7</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>51.97561803480375</v>
+        <v>38.92943837935411</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>10.34922810529716</v>
+        <v>17.68460429279206</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.1870308286568034</v>
+        <v>0.4343049842883785</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.5986346228013717</v>
+        <v>0.2286166760005388</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>7823</v>
+        <v>7765</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>奧義賽博-KY創</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>210.2021684612833</v>
+        <v>216.3725253644933</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>80.90000000000001</v>
+        <v>222</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>37.36929312220279</v>
+        <v>37.56840364739835</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>30.84584470823703</v>
+        <v>25.76197963059441</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1.458313994624355</v>
+        <v>0.6475372202262271</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.0015999116167724</v>
+        <v>-1.866134535011144</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>8011</v>
+        <v>8038</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>208.6856095802565</v>
+        <v>215.5568288754205</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>18</v>
+        <v>40.15</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>49.71707715081734</v>
+        <v>47.65131632623464</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>15.55705778833168</v>
+        <v>6.795267021245061</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.7530642590691052</v>
+        <v>0.5478853360697563</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.0333193253363687</v>
+        <v>-0.0253454598029686</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>7721</v>
+        <v>6855</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>199.6493564736794</v>
+        <v>211.7157055573561</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>75.59999999999999</v>
+        <v>121</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>51.29610229775329</v>
+        <v>51.97561803480375</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>12.68283530527054</v>
+        <v>10.34922810529716</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.4384524471617175</v>
+        <v>0.1870308286568034</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.2166635988731085</v>
+        <v>0.5986346228013717</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>7791</v>
+        <v>7823</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>皇家可口</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>197.5147984862211</v>
+        <v>210.2021684612833</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>62.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>46.32601301219925</v>
+        <v>37.36929312220279</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>15.20411607075842</v>
+        <v>30.84584470823703</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.3749976481339623</v>
+        <v>1.458313994624355</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.0233292845201742</v>
+        <v>-0.0015999116167724</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>7730</v>
+        <v>8011</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>196.3475051091564</v>
+        <v>208.6856095802565</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>191.5</v>
+        <v>18</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>54.70013007050652</v>
+        <v>49.71707715081734</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>11.41509162772088</v>
+        <v>15.55705778833168</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.967807956377965</v>
+        <v>0.7530642590691052</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>1.318164826638035</v>
+        <v>0.0333193253363687</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, breakout_20d, market_above_ma60, cci_momentum</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>7750</v>
+        <v>7721</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>新代</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>195.850721296144</v>
+        <v>199.6493564736794</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>2195</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>50.08281954740725</v>
+        <v>51.29610229775329</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>18.91215051970794</v>
+        <v>12.68283530527054</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.5867379686472541</v>
+        <v>0.4384524471617175</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-1.962802173904244</v>
+        <v>-0.2166635988731085</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6877</v>
+        <v>7791</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>皇家可口</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>195.2912511234572</v>
+        <v>197.5147984862211</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>136.5</v>
+        <v>62.7</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>48.74706018601847</v>
+        <v>46.32601301219925</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>16.34605024957974</v>
+        <v>15.20411607075842</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.5367587270193964</v>
+        <v>0.3749976481339623</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>1.322688283999459</v>
+        <v>0.0233292845201742</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>7732</v>
+        <v>7730</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>金興精密</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>180.3223083687187</v>
+        <v>196.3475051091564</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>35.65</v>
+        <v>191.5</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>51.761539277057</v>
+        <v>54.70013007050652</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>13.02906742218241</v>
+        <v>11.41509162772088</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.1672361574090502</v>
+        <v>0.967807956377965</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.7646877021785103</v>
+        <v>1.318164826638035</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, breakout_20d, market_above_ma60, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>8034</v>
+        <v>7750</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>新代</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>167.9823059976875</v>
+        <v>195.850721296144</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>22.1</v>
+        <v>2195</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>35.46914719282445</v>
+        <v>50.08281954740725</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>23.62335530037556</v>
+        <v>18.91215051970794</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.4918400909596392</v>
+        <v>0.5867379686472541</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.1179663721363403</v>
+        <v>-1.962802173904244</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>7803</v>
+        <v>6877</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>164.7816034921215</v>
+        <v>195.2912511234572</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>23.8</v>
+        <v>136.5</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>50.23311161317132</v>
+        <v>48.74706018601847</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>16.44336482917433</v>
+        <v>16.34605024957974</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1.553687478148743</v>
+        <v>0.5367587270193964</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.3813356024094021</v>
+        <v>1.322688283999459</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6997</v>
+        <v>7732</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>金興精密</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>161.4806292622452</v>
+        <v>180.3223083687187</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>72</v>
+        <v>35.65</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>50.60362051950337</v>
+        <v>51.761539277057</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>6.907832920905761</v>
+        <v>13.02906742218241</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.281160903574823</v>
+        <v>0.1672361574090502</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.092016336969013</v>
+        <v>0.7646877021785103</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6936</v>
+        <v>8034</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>156.846870430168</v>
+        <v>167.9823059976875</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>32.9</v>
+        <v>22.1</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>46.39555484717408</v>
+        <v>35.46914719282445</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>13.23467538238057</v>
+        <v>23.62335530037556</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.217863301175627</v>
+        <v>0.4918400909596392</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.0030217153025668</v>
+        <v>-0.1179663721363403</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6918</v>
+        <v>7803</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>雲象科技-創</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>156.5443643806956</v>
+        <v>164.7816034921215</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>73.5</v>
+        <v>23.8</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>50.16990727843459</v>
+        <v>50.23311161317132</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>6.682524862184697</v>
+        <v>16.44336482917433</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>1.324935873842111</v>
+        <v>1.553687478148743</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.0014937121037975</v>
+        <v>0.3813356024094021</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>7740</v>
+        <v>6997</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>博弘</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>147.8935960416526</v>
+        <v>161.4806292622452</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>150</v>
+        <v>72</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,16 +6647,16 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>40.46177999386055</v>
+        <v>50.60362051950337</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>18.10222644712152</v>
+        <v>6.907832920905761</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.4718199522330151</v>
+        <v>1.281160903574823</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.692360033068816</v>
+        <v>0.092016336969013</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6895</v>
+        <v>6936</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>145.5623138741761</v>
+        <v>156.846870430168</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>148</v>
+        <v>32.9</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>42.67305619602146</v>
+        <v>46.39555484717408</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>16.16729319970488</v>
+        <v>13.23467538238057</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.2889531598823512</v>
+        <v>1.217863301175627</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-1.373537070208447</v>
+        <v>-0.0030217153025668</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>7736</v>
+        <v>6918</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>145.3145010849532</v>
+        <v>156.5443643806956</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>70.8</v>
+        <v>73.5</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>41.43336930029274</v>
+        <v>50.16990727843459</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>12.51064661996858</v>
+        <v>6.682524862184697</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.9561834041146404</v>
+        <v>1.324935873842111</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.0515713455822758</v>
+        <v>-0.0014937121037975</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6781,21 +6781,21 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6908</v>
+        <v>7740</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>宏碁遊戲-創</t>
+          <t>熙特爾-創</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>143.6348329646843</v>
+        <v>147.8935960416526</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>38</v>
+        <v>150</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>44.72323463234895</v>
+        <v>40.46177999386055</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>12.03597150956111</v>
+        <v>18.10222644712152</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>1.204840624390935</v>
+        <v>0.4718199522330151</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.0380664026556524</v>
+        <v>-0.692360033068816</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>7780</v>
+        <v>6895</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>136.1797156765973</v>
+        <v>145.5623138741761</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>18.35</v>
+        <v>148</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>49.04000315313512</v>
+        <v>42.67305619602146</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>15.47780285382028</v>
+        <v>16.16729319970488</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.6266448006778184</v>
+        <v>0.2889531598823512</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.0116709437831915</v>
+        <v>-1.373537070208447</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6925</v>
+        <v>7736</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>意藍</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>109.626939426204</v>
+        <v>145.3145010849532</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>61.2</v>
+        <v>70.8</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>45.46519739769212</v>
+        <v>41.43336930029274</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>14.40348122888705</v>
+        <v>12.51064661996858</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.1818383948725632</v>
+        <v>0.9561834041146404</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.3139404126089351</v>
+        <v>-0.0515713455822758</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6923</v>
+        <v>6908</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>宏碁遊戲-創</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>66.82044136816546</v>
+        <v>143.6348329646843</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>49.70159526845657</v>
+        <v>44.72323463234895</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>13.12127307402995</v>
+        <v>12.03597150956111</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>1.078183046582787</v>
+        <v>1.204840624390935</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.0835476596536235</v>
+        <v>-0.0380664026556524</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6885</v>
+        <v>7780</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>14.01205445363154</v>
+        <v>136.1797156765973</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>21.85</v>
+        <v>18.35</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>47.14543188586586</v>
+        <v>49.04000315313512</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>17.24124814094029</v>
+        <v>15.47780285382028</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.3811112015673893</v>
+        <v>0.6266448006778184</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,62 +7036,221 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.0756296889895671</v>
+        <v>-0.0116709437831915</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
+        <v>6925</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>意藍</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>109.626939426204</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>45.46519739769212</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>14.40348122888705</v>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>0.1818383948725632</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>-0.3139404126089351</v>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>6923</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>中台</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>66.82044136816546</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>49.70159526845657</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>13.12127307402995</v>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>1.078183046582787</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>-0.0835476596536235</v>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>6885</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>全福生技</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>14.01205445363154</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>21.85</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>47.14543188586586</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>17.24124814094029</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>0.3811112015673893</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>-0.0756296889895671</v>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
         <v>6873</v>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>泓德能源</t>
         </is>
       </c>
-      <c r="C125" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D125" s="2" t="n">
+      <c r="C128" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D128" s="2" t="n">
         <v>7.679151531694841</v>
       </c>
-      <c r="E125" s="2" t="n">
+      <c r="E128" s="2" t="n">
         <v>86.09999999999999</v>
       </c>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G125" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H125" s="2" t="n">
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" s="2" t="n">
         <v>54.03830525810871</v>
       </c>
-      <c r="I125" s="2" t="n">
+      <c r="I128" s="2" t="n">
         <v>12.15970972215359</v>
       </c>
-      <c r="J125" s="2" t="n">
+      <c r="J128" s="2" t="n">
         <v>1.49532951738859</v>
       </c>
-      <c r="K125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M125" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N125" s="2" t="n">
+      <c r="K128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N128" s="2" t="n">
         <v>0.5295391174201143</v>
       </c>
-      <c r="O125" s="2" t="inlineStr">
+      <c r="O128" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60</t>
         </is>
